--- a/event_evaluation_forms/038_event_completion_report_form--event_evaluation_forms.xlsx
+++ b/event_evaluation_forms/038_event_completion_report_form--event_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -598,7 +598,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Event Outcomes</t>
+          <t>Event Outcomes (2)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -616,12 +616,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>event_feedback</t>
+          <t>event_feedback_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Event Feedback</t>
+          <t>Event Feedback 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -961,12 +961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>evaluation_form_completion_status</t>
+          <t>evaluation_form_completion_status_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Evaluation Form Completion Status</t>
+          <t>Evaluation Form Completion Status 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1181,7 +1181,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>event_feedback_choices</t>
+          <t>event_feedback_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1198,7 +1198,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>event_feedback_choices</t>
+          <t>event_feedback_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>event_feedback_choices</t>
+          <t>event_feedback_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1334,7 +1334,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>evaluation_form_completion_status_choices</t>
+          <t>evaluation_form_completion_status_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>evaluation_form_completion_status_choices</t>
+          <t>evaluation_form_completion_status_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>evaluation_form_completion_status_choices</t>
+          <t>evaluation_form_completion_status_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
